--- a/tests/Mixed Duet.xlsx
+++ b/tests/Mixed Duet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Synchro\Coach Card\Sheets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\leahy\RustroverProjects\check_cards\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F2596EA-D830-484C-BF6E-4A76C09176E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EAC16BD-5B6E-477E-8988-E7DB0450CC72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{34322A2D-AD5A-426D-8F2B-FDA4DB54FF9C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{34322A2D-AD5A-426D-8F2B-FDA4DB54FF9C}"/>
   </bookViews>
   <sheets>
     <sheet name="SENIOR-Mixed_Duet_Free-PRELIMS" sheetId="1" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>ReqHY</t>
   </si>
   <si>
-    <t xml:space="preserve"> T9a CB C3</t>
-  </si>
-  <si>
     <t>9CE2</t>
   </si>
   <si>
@@ -136,6 +133,9 @@
   </si>
   <si>
     <t>ISS Coach Card Version: 3.0.2</t>
+  </si>
+  <si>
+    <t>T9 CB C3</t>
   </si>
 </sst>
 </file>
@@ -284,21 +284,7 @@
   </cellStyleXfs>
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -309,6 +295,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -318,15 +313,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -662,693 +662,700 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE7F1935-4E7F-48AA-9D34-E1622E90380A}">
   <dimension ref="A1:H60"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="10.77734375" customWidth="1"/>
-    <col min="3" max="3" width="6.77734375" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" customWidth="1"/>
-    <col min="5" max="5" width="27.77734375" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" customWidth="1"/>
-    <col min="7" max="7" width="10.77734375" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" customWidth="1"/>
+    <col min="1" max="2" width="10.796875" customWidth="1"/>
+    <col min="3" max="3" width="6.796875" customWidth="1"/>
+    <col min="4" max="4" width="10.796875" customWidth="1"/>
+    <col min="5" max="5" width="27.796875" customWidth="1"/>
+    <col min="6" max="6" width="9.796875" customWidth="1"/>
+    <col min="7" max="7" width="10.796875" customWidth="1"/>
+    <col min="8" max="8" width="6.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="45" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="3"/>
-    </row>
-    <row r="2" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="21"/>
+    </row>
+    <row r="2" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="8"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="7" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A6" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="8"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="7" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="9" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="10" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="14" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="16"/>
-    </row>
-    <row r="10" spans="1:8" ht="29.4" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="11" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" ht="28.9" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+    <row r="11" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="20"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="7">
         <v>1</v>
       </c>
-      <c r="D12" s="18"/>
-      <c r="E12" s="17" t="s">
+      <c r="D12" s="7"/>
+      <c r="E12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="8">
+        <v>3</v>
+      </c>
+      <c r="H12" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19">
-        <v>3</v>
-      </c>
-      <c r="H12" s="21" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A13" s="7" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
+      <c r="B13" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="C13" s="7">
+        <v>2</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="18">
-        <v>2</v>
-      </c>
-      <c r="D13" s="18"/>
-      <c r="E13" s="17" t="s">
+      <c r="F13" s="6"/>
+      <c r="G13" s="8">
+        <v>2.25</v>
+      </c>
+      <c r="H13" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="19">
-        <v>2.25</v>
-      </c>
-      <c r="H13" s="21" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A14" s="7"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="9"/>
+    </row>
+    <row r="15" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A15" s="7"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="9"/>
+    </row>
+    <row r="16" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="7"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="9"/>
+    </row>
+    <row r="17" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A17" s="7"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="9"/>
+    </row>
+    <row r="18" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="7"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="9"/>
+    </row>
+    <row r="19" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A19" s="7"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A20" s="7"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="9"/>
+    </row>
+    <row r="21" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A21" s="7"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="9"/>
+    </row>
+    <row r="22" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="7"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A23" s="7"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="7"/>
+      <c r="D23" s="7"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="9"/>
+    </row>
+    <row r="24" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A24" s="7"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="9"/>
+    </row>
+    <row r="25" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A25" s="7"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="9"/>
+    </row>
+    <row r="26" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A26" s="7"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="9"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A27" s="7"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="9"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A28" s="7"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="8"/>
+      <c r="H28" s="9"/>
+    </row>
+    <row r="29" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A29" s="7"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
+    </row>
+    <row r="30" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="7"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="9"/>
+    </row>
+    <row r="31" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A31" s="7"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="7"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="9"/>
+    </row>
+    <row r="32" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A32" s="7"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="7"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="9"/>
+    </row>
+    <row r="33" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A33" s="7"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="9"/>
+    </row>
+    <row r="34" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A34" s="7"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="9"/>
+    </row>
+    <row r="35" spans="1:8" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A35" s="7"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="7"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="9"/>
+    </row>
+    <row r="36" spans="1:8" ht="14.65" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="18"/>
-      <c r="B14" s="17"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="20"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="18"/>
-      <c r="B15" s="17"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="20"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18"/>
-      <c r="B16" s="17"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="20"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="18"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="20"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="18"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="20"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="18"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="20"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="18"/>
-      <c r="B20" s="17"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="20"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="18"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="20"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="18"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="18"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="19"/>
-      <c r="H23" s="20"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="18"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="20"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="18"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="19"/>
-      <c r="H25" s="20"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="18"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="19"/>
-      <c r="H26" s="20"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="18"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="17"/>
-      <c r="G27" s="19"/>
-      <c r="H27" s="20"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="18"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="20"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="18"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="19"/>
-      <c r="H29" s="20"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="18"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="18"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="19"/>
-      <c r="H30" s="20"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="18"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="19"/>
-      <c r="H31" s="20"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="18"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="19"/>
-      <c r="H32" s="20"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="18"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="17"/>
-      <c r="F33" s="17"/>
-      <c r="G33" s="19"/>
-      <c r="H33" s="20"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="18"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="20"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.6" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="18"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="18"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="20"/>
-    </row>
-    <row r="36" spans="1:8" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="4" t="s">
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-      <c r="B41" s="4"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="4"/>
-      <c r="H41" s="4"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="4"/>
-      <c r="B42" s="4"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="4"/>
-      <c r="H42" s="4"/>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="4"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="4"/>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="4"/>
-      <c r="B45" s="4"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="4"/>
-      <c r="B48" s="4"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="4"/>
-      <c r="B49" s="4"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="4"/>
-      <c r="H49" s="4"/>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4"/>
-      <c r="B50" s="4"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="4"/>
-      <c r="H50" s="4"/>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="4"/>
-      <c r="B51" s="4"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="4"/>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="4"/>
-      <c r="B52" s="4"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="4"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="4"/>
-      <c r="B53" s="4"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="4"/>
-      <c r="H53" s="4"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="4"/>
-      <c r="B54" s="4"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="4"/>
-      <c r="H54" s="4"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="4"/>
-      <c r="H55" s="4"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="4"/>
-      <c r="H56" s="4"/>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="4"/>
-      <c r="B57" s="4"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="4"/>
-      <c r="H57" s="4"/>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="4"/>
-      <c r="B58" s="4"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="4"/>
-      <c r="H58" s="4"/>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="4"/>
-      <c r="B59" s="4"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="4"/>
-      <c r="H59" s="4"/>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="4"/>
-      <c r="B60" s="4"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="4"/>
-      <c r="H60" s="4"/>
+      <c r="B39" s="1"/>
+      <c r="C39" s="1"/>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A40" s="1"/>
+      <c r="B40" s="1"/>
+      <c r="C40" s="1"/>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A41" s="1"/>
+      <c r="B41" s="1"/>
+      <c r="C41" s="1"/>
+      <c r="D41" s="1"/>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1"/>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1"/>
+      <c r="D43" s="1"/>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1"/>
+      <c r="D44" s="1"/>
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="1"/>
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="1"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="1"/>
+      <c r="H49" s="1"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+      <c r="G50" s="1"/>
+      <c r="H50" s="1"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="1"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="1"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="D3:H3"/>
     <mergeCell ref="A9:H9"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
@@ -1356,13 +1363,6 @@
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="D7:H7"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:H4"/>
   </mergeCells>
   <pageMargins left="6.9444444444444441E-3" right="6.9444444444444441E-3" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
